--- a/data/trending_integrated_20261008_14.xlsx
+++ b/data/trending_integrated_20261008_14.xlsx
@@ -584,7 +584,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31062922310</v>
+        <v>31070790880</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11510</v>
+        <v>11550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.50%</t>
+          <t>'+16.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>64609109960</v>
+        <v>65135133700</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -762,13 +762,13 @@
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F4" t="n">
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>47690131275</v>
+        <v>48146839825</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15520</v>
+        <v>15490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.55%</t>
+          <t>'+12.33%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="F5" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G5" t="n">
-        <v>1505</v>
+        <v>1533</v>
       </c>
       <c r="H5" t="n">
         <v>0.09</v>
@@ -886,7 +886,7 @@
         <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>180504379130</v>
+        <v>186595706525</v>
       </c>
       <c r="P5" t="n">
         <v>28700</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38050</v>
+        <v>38250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.11%</t>
+          <t>'+5.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H6" t="n">
         <v>31.86</v>
@@ -978,7 +978,7 @@
         <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>123556595525</v>
+        <v>124298570450</v>
       </c>
       <c r="P6" t="n">
         <v>45000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13190</v>
+        <v>13250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.93%</t>
+          <t>'+5.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
         <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="H7" t="n">
         <v>1.07</v>
@@ -1070,7 +1070,7 @@
         <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>84562857835</v>
+        <v>84946414665</v>
       </c>
       <c r="P7" t="n">
         <v>22250</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6690</v>
+        <v>6730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.56%</t>
+          <t>'+4.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>8390</v>
       </c>
       <c r="M8" t="n">
-        <v>6680</v>
+        <v>6540</v>
       </c>
       <c r="N8" t="n">
         <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>21034459960</v>
+        <v>21242092610</v>
       </c>
       <c r="P8" t="n">
         <v>9680</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4445</v>
+        <v>46000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.34%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.19</v>
+        <v>-0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>323</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>175</v>
       </c>
       <c r="G9" t="n">
-        <v>189</v>
+        <v>1194</v>
       </c>
       <c r="H9" t="n">
-        <v>4.46</v>
+        <v>13.39</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4430</v>
+        <v>45900</v>
       </c>
       <c r="K9" t="n">
-        <v>4650</v>
+        <v>45950</v>
       </c>
       <c r="L9" t="n">
-        <v>4855</v>
+        <v>46500</v>
       </c>
       <c r="M9" t="n">
-        <v>4185</v>
+        <v>45100</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>14.12</v>
       </c>
       <c r="O9" t="n">
-        <v>88863929585</v>
+        <v>33502307700</v>
       </c>
       <c r="P9" t="n">
-        <v>5470</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>2810</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-471000</v>
+        <v>-66000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 기대감과 2026년 연말 30만 목표 주가가 언급되며, 공매도 세력에 대한 경고와 함께 무상증자 및 신한증권 관련 논의가 있음.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', '페스트']</t>
+          <t>['HLB', '리보세라닙', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1720000</v>
+        <v>8260</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.17%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>456</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>1576</v>
+        <v>267</v>
       </c>
       <c r="H10" t="n">
-        <v>49.59</v>
+        <v>26.38</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,143 +1331,143 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1723000</v>
+        <v>8250</v>
       </c>
       <c r="K10" t="n">
-        <v>1722000</v>
+        <v>8190</v>
       </c>
       <c r="L10" t="n">
-        <v>1759000</v>
+        <v>8320</v>
       </c>
       <c r="M10" t="n">
-        <v>1692000</v>
+        <v>8090</v>
       </c>
       <c r="N10" t="n">
-        <v>49.71</v>
+        <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3321931371500</v>
+        <v>16894644175</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>403000</v>
+        <v>8090</v>
       </c>
       <c r="R10" t="n">
-        <v>82000</v>
+        <v>-51000</v>
       </c>
       <c r="S10" t="n">
-        <v>-70000</v>
+        <v>111000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 및 국내 증시 상황에 대한 불만. 솔리다임 상장 이슈 및 정치적 비판.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가', '증시']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45750</v>
+        <v>1724000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.33%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>319</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>174</v>
+        <v>452</v>
       </c>
       <c r="G11" t="n">
-        <v>1183</v>
+        <v>1588</v>
       </c>
       <c r="H11" t="n">
-        <v>13.39</v>
+        <v>49.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>45900</v>
+        <v>1723000</v>
       </c>
       <c r="K11" t="n">
-        <v>45950</v>
+        <v>1722000</v>
       </c>
       <c r="L11" t="n">
-        <v>46500</v>
+        <v>1759000</v>
       </c>
       <c r="M11" t="n">
-        <v>45100</v>
+        <v>1692000</v>
       </c>
       <c r="N11" t="n">
-        <v>14.12</v>
+        <v>49.71</v>
       </c>
       <c r="O11" t="n">
-        <v>32492625950</v>
+        <v>3393204241500</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>403000</v>
       </c>
       <c r="R11" t="n">
-        <v>-66000</v>
+        <v>82000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 기대감과 2026년 연말 30만 목표 주가가 언급되며, 공매도 세력에 대한 경고와 함께 무상증자 및 신한증권 관련 논의가 있음.</t>
+          <t>솔리다임 상장 관련 논란 및 주가 조작 의혹 제기, 외국인 매도세 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['HLB', '리보세라닙', '공매도']</t>
+          <t>['솔리다임', '상장', '외국인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>267000</v>
+        <v>267500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G12" t="n">
-        <v>2045</v>
+        <v>2121</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>3441358904000</v>
+        <v>3534275733750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18930</v>
+        <v>4370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-1.35%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G13" t="n">
-        <v>369</v>
+        <v>192</v>
       </c>
       <c r="H13" t="n">
-        <v>27.68</v>
+        <v>4.46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19540</v>
+        <v>4430</v>
       </c>
       <c r="K13" t="n">
-        <v>19490</v>
+        <v>4650</v>
       </c>
       <c r="L13" t="n">
-        <v>19500</v>
+        <v>4855</v>
       </c>
       <c r="M13" t="n">
-        <v>18850</v>
+        <v>4185</v>
       </c>
       <c r="N13" t="n">
-        <v>27.67</v>
+        <v>3.27</v>
       </c>
       <c r="O13" t="n">
-        <v>43425046600</v>
+        <v>89211181375</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>5470</v>
       </c>
       <c r="Q13" t="n">
-        <v>18440</v>
+        <v>2810</v>
       </c>
       <c r="R13" t="n">
-        <v>-451000</v>
+        <v>-471000</v>
       </c>
       <c r="S13" t="n">
-        <v>-69000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조선주 폭락의 주범으로 특정 세력 지목 및 애널리스트들의 추천 종목 손실 발생에 대한 비판. 선박 뉴스 신뢰도 의문 제기 및 페인트 회사 주가 미반영 등 실질적 근거 부족에 따른 부정적 전망.</t>
+          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '폭락', '실적']</t>
+          <t>['항생제', '폐렴', '페스트']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>232500</v>
+        <v>18970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-2.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>815</v>
+        <v>376</v>
       </c>
       <c r="H14" t="n">
-        <v>3.47</v>
+        <v>27.68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>241000</v>
+        <v>19540</v>
       </c>
       <c r="K14" t="n">
-        <v>227000</v>
+        <v>19490</v>
       </c>
       <c r="L14" t="n">
-        <v>239500</v>
+        <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>210500</v>
+        <v>18850</v>
       </c>
       <c r="N14" t="n">
-        <v>4.12</v>
+        <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>43461576750</v>
+        <v>44567498915</v>
       </c>
       <c r="P14" t="n">
-        <v>1233000</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>120000</v>
+        <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>6000</v>
+        <v>-451000</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>-69000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼천당제약의 아일리아 영업이익 전망 및 연기금 매수세 유입. 공매도 과열 및 릴레이 계약 공시 기대.</t>
+          <t>조선주 폭락 및 실적 기대와 달리 손실 발생, 금리 인상 및 수주 취소 우려 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['아일리아', '영업이익', '계약공시']</t>
+          <t>['조선주', '실적', '수주']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16710</v>
+        <v>16750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F15" t="n">
         <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>41919975135</v>
+        <v>42699470880</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1851,92 +1851,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8260</v>
+        <v>231500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.29%</t>
+          <t>'-3.94%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.17</v>
+        <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="G16" t="n">
-        <v>267</v>
+        <v>842</v>
       </c>
       <c r="H16" t="n">
-        <v>26.38</v>
+        <v>3.47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8630</v>
+        <v>241000</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>227000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>239500</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>210500</v>
       </c>
       <c r="N16" t="n">
-        <v>26.55</v>
+        <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>16610000000</v>
+        <v>44454008500</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1233000</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="R16" t="n">
-        <v>-51000</v>
+        <v>6000</v>
       </c>
       <c r="S16" t="n">
-        <v>111000</v>
+        <v>5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>연기금 매수세 유입 및 신규 계약 공시 기대, 캐나다 세마 및 경구 인슐린 관련주로서의 전망 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['연기금', '계약공시', '경구인슐린']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28300</v>
+        <v>28400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.03%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>72</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H17" t="n">
         <v>10.02</v>
@@ -1990,7 +1990,7 @@
         <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>63035382225</v>
+        <v>64025565950</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16960</v>
+        <v>17050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-4.96%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F18" t="n">
         <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>95342497660</v>
+        <v>96238539370</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75600</v>
+        <v>75500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.09%</t>
+          <t>'-6.21%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>443</v>
       </c>
       <c r="F19" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G19" t="n">
-        <v>1294</v>
+        <v>1328</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2174,7 +2174,7 @@
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>206492744950</v>
+        <v>210605558150</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 텍사스 가스발전 확정 소식과 원전 관련 언급. 주가 하락 및 공매도에 대한 부정적 감정 표현.</t>
+          <t>국내 가스 발전 수주 및 원전 건설 기대 언급, 그러나 주가 하락 및 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['가스발전', '원전', '수주']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4860</v>
+        <v>4865</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.72%</t>
+          <t>'-6.62%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H20" t="n">
         <v>4.65</v>
@@ -2266,7 +2266,7 @@
         <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>68880394532</v>
+        <v>69555206144</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15250</v>
+        <v>15290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.74%</t>
+          <t>'-8.50%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-1.44</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H21" t="n">
         <v>0.93</v>
@@ -2358,7 +2358,7 @@
         <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>35452022290</v>
+        <v>35645875105</v>
       </c>
       <c r="P21" t="n">
         <v>17590</v>
@@ -2403,83 +2403,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7130</v>
+        <v>52700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.82%</t>
+          <t>'-9.29%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-2.03</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>197</v>
+        <v>342</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>163</v>
       </c>
       <c r="G22" t="n">
-        <v>582</v>
+        <v>689</v>
       </c>
       <c r="H22" t="n">
-        <v>3.09</v>
+        <v>1.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7820</v>
+        <v>58100</v>
       </c>
       <c r="K22" t="n">
-        <v>8080</v>
+        <v>63200</v>
       </c>
       <c r="L22" t="n">
-        <v>8510</v>
+        <v>63800</v>
       </c>
       <c r="M22" t="n">
-        <v>7060</v>
+        <v>51700</v>
       </c>
       <c r="N22" t="n">
-        <v>5.12</v>
+        <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>85617973925</v>
+        <v>56906800150</v>
       </c>
       <c r="P22" t="n">
-        <v>23500</v>
+        <v>63800</v>
       </c>
       <c r="Q22" t="n">
-        <v>2890</v>
+        <v>25600</v>
       </c>
       <c r="R22" t="n">
-        <v>-518000</v>
+        <v>-173000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼표시멘트의 본PF 대주단 구성 중 소식 및 성수동 땅값 언급. 주가 급등 가능성에 대한 기대와 분석.</t>
+          <t>비만약 승인 및 기술 수출에도 불구하고 급락, 주가 조작 및 개미 털기 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '땅값']</t>
+          <t>['비만약', '기술수출', '주가조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52700</v>
+        <v>7080</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.29%</t>
+          <t>'-9.46%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.02</v>
+        <v>-2.03</v>
       </c>
       <c r="E23" t="n">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="F23" t="n">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="G23" t="n">
-        <v>681</v>
+        <v>588</v>
       </c>
       <c r="H23" t="n">
-        <v>1.32</v>
+        <v>3.09</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>58100</v>
+        <v>7820</v>
       </c>
       <c r="K23" t="n">
-        <v>63200</v>
+        <v>8080</v>
       </c>
       <c r="L23" t="n">
-        <v>63800</v>
+        <v>8510</v>
       </c>
       <c r="M23" t="n">
-        <v>51700</v>
+        <v>7050</v>
       </c>
       <c r="N23" t="n">
-        <v>1.3</v>
+        <v>5.12</v>
       </c>
       <c r="O23" t="n">
-        <v>56325016600</v>
+        <v>86423645160</v>
       </c>
       <c r="P23" t="n">
-        <v>63800</v>
+        <v>23500</v>
       </c>
       <c r="Q23" t="n">
-        <v>25600</v>
+        <v>2890</v>
       </c>
       <c r="R23" t="n">
-        <v>-173000</v>
+        <v>-518000</v>
       </c>
       <c r="S23" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>한미사이언스의 기술 수출 및 식약처 승인에도 불구하고 주가 급락한 상황에 대한 비판. 주가 조작 및 차명 거래 의심.</t>
+          <t>삼표시멘트의 본PF 대주단 구성 중 소식 및 성수동 땅값 언급. 주가 급등 가능성에 대한 기대와 분석.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['기술수출', '식약처 승인', '주가 조작']</t>
+          <t>['본PF', '대주단', '땅값']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9800</v>
+        <v>9830</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.99%</t>
+          <t>'-10.72%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F24" t="n">
         <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>7220727695</v>
+        <v>7251422775</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_14.xlsx
+++ b/data/trending_integrated_20261008_14.xlsx
@@ -584,7 +584,7 @@
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31070790880</v>
+        <v>31075005960</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -670,7 +670,7 @@
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
@@ -693,7 +693,7 @@
         <v>10030</v>
       </c>
       <c r="L3" t="n">
-        <v>11570</v>
+        <v>11600</v>
       </c>
       <c r="M3" t="n">
         <v>9850</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>65135133700</v>
+        <v>66258062655</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -711,10 +711,10 @@
         <v>3445</v>
       </c>
       <c r="R3" t="n">
-        <v>197000</v>
+        <v>133000</v>
       </c>
       <c r="S3" t="n">
-        <v>452000</v>
+        <v>508000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13740</v>
+        <v>13780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.60%</t>
+          <t>'+14.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>48146839825</v>
+        <v>48733675685</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -803,10 +803,10 @@
         <v>6500</v>
       </c>
       <c r="R4" t="n">
-        <v>-3000</v>
+        <v>-23000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5000</v>
+        <v>-39000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15490</v>
+        <v>15280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.33%</t>
+          <t>'+10.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="F5" t="n">
         <v>251</v>
       </c>
       <c r="G5" t="n">
-        <v>1533</v>
+        <v>1564</v>
       </c>
       <c r="H5" t="n">
         <v>0.09</v>
@@ -886,7 +886,7 @@
         <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>186595706525</v>
+        <v>191871310320</v>
       </c>
       <c r="P5" t="n">
         <v>28700</v>
@@ -895,7 +895,7 @@
         <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>26000</v>
+        <v>-22000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38250</v>
+        <v>13250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.66%</t>
+          <t>'+5.41%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K6" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L6" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M6" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O6" t="n">
-        <v>124298570450</v>
+        <v>85199505075</v>
       </c>
       <c r="P6" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q6" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R6" t="n">
-        <v>221000</v>
+        <v>-550000</v>
       </c>
       <c r="S6" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
+          <t>유증 물량 정리 및 매물대 언급. 주가 상승에 대한 기대감과 함께, 변동성에 대한 우려와 기대감 혼재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기관 매수', '외국인 매수', '추세']</t>
+          <t>['유증', '매물대']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13250</v>
+        <v>38150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.41%</t>
+          <t>'+5.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>14200</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>84946414665</v>
+        <v>125372595000</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-501000</v>
+        <v>247000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB제약의 주가 상승 기대감과 목표 주가 제시가 있으나, 일부에서는 주가 움직임이 답답하다는 의견과 함께 유증 물량 정리 및 공매도 관련 논의가 있음.</t>
+          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['HLB제약', '목표 주가', '유증']</t>
+          <t>['기관 매수', '외국인 매수', '추세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6730</v>
+        <v>6610</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+2.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>21242092610</v>
+        <v>21345967830</v>
       </c>
       <c r="P8" t="n">
         <v>9680</v>
@@ -1171,7 +1171,7 @@
         <v>371</v>
       </c>
       <c r="R8" t="n">
-        <v>-27000</v>
+        <v>-28000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46000</v>
+        <v>46100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G9" t="n">
-        <v>1194</v>
+        <v>1228</v>
       </c>
       <c r="H9" t="n">
         <v>13.39</v>
@@ -1254,7 +1254,7 @@
         <v>14.12</v>
       </c>
       <c r="O9" t="n">
-        <v>33502307700</v>
+        <v>34388506375</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1263,10 +1263,10 @@
         <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-66000</v>
+        <v>-53000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8260</v>
+        <v>8280</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H10" t="n">
         <v>26.38</v>
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>16894644175</v>
+        <v>17302844765</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1355,10 +1355,10 @@
         <v>8090</v>
       </c>
       <c r="R10" t="n">
-        <v>-51000</v>
+        <v>-17000</v>
       </c>
       <c r="S10" t="n">
-        <v>111000</v>
+        <v>149000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1724000</v>
+        <v>1726000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G11" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="H11" t="n">
         <v>49.59</v>
@@ -1438,7 +1438,7 @@
         <v>49.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3393204241500</v>
+        <v>3445369388500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1447,10 +1447,10 @@
         <v>403000</v>
       </c>
       <c r="R11" t="n">
-        <v>82000</v>
+        <v>17000</v>
       </c>
       <c r="S11" t="n">
-        <v>-70000</v>
+        <v>-84000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>267500</v>
+        <v>267000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="G12" t="n">
-        <v>2121</v>
+        <v>2166</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>3534275733750</v>
+        <v>3597981017250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1539,23 +1539,23 @@
         <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>78000</v>
+        <v>56000</v>
       </c>
       <c r="S12" t="n">
-        <v>-934000</v>
+        <v>-965000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자의 높은 영업이익에도 불구하고 주가 부양 없는 현실에 대한 불만. 정치적 이슈와 증시 정책에 대한 비판.</t>
+          <t>정치적 이슈와 증시 상황에 대한 불만 표출. 실적 대비 주가 부양 부재에 대한 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '증시', '정치']</t>
+          <t>['주가 부양', '국내 증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4370</v>
+        <v>4365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.35%</t>
+          <t>'-1.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H13" t="n">
         <v>4.46</v>
@@ -1622,7 +1622,7 @@
         <v>3.27</v>
       </c>
       <c r="O13" t="n">
-        <v>89211181375</v>
+        <v>90441090340</v>
       </c>
       <c r="P13" t="n">
         <v>5470</v>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18970</v>
+        <v>18990</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
         <v>376</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>44567498915</v>
+        <v>45275379110</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1723,10 +1723,10 @@
         <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>-451000</v>
+        <v>-449000</v>
       </c>
       <c r="S14" t="n">
-        <v>-69000</v>
+        <v>-78000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16750</v>
+        <v>16780</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>42699470880</v>
+        <v>43414994645</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1815,10 +1815,10 @@
         <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-81000</v>
+        <v>-58000</v>
       </c>
       <c r="S15" t="n">
-        <v>-19000</v>
+        <v>-36000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1866,13 +1866,13 @@
         <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F16" t="n">
         <v>73</v>
       </c>
       <c r="G16" t="n">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="H16" t="n">
         <v>3.47</v>
@@ -1898,7 +1898,7 @@
         <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>44454008500</v>
+        <v>45432856750</v>
       </c>
       <c r="P16" t="n">
         <v>1233000</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연기금 매수세 유입 및 신규 계약 공시 기대, 캐나다 세마 및 경구 인슐린 관련주로서의 전망 제기.</t>
+          <t>공매도 과열 종목 지정 및 연기금 매수세 확인. 신규 계약 공시 및 바이오 업황 호조 기대감. 3연상 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['연기금', '계약공시', '경구인슐린']</t>
+          <t>['공매도 금지', '계약 공시', '바이오']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,184 +1943,184 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28400</v>
+        <v>17070</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-4.85%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>-0.95</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="G17" t="n">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="H17" t="n">
-        <v>10.02</v>
+        <v>3.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>17940</v>
       </c>
       <c r="K17" t="n">
-        <v>29900</v>
+        <v>17770</v>
       </c>
       <c r="L17" t="n">
-        <v>30000</v>
+        <v>17940</v>
       </c>
       <c r="M17" t="n">
-        <v>28050</v>
+        <v>16750</v>
       </c>
       <c r="N17" t="n">
-        <v>10.78</v>
+        <v>4.92</v>
       </c>
       <c r="O17" t="n">
-        <v>64025565950</v>
+        <v>97116231310</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-560000</v>
+        <v>-412000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>-70000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>대한광통신의 주가 하락 및 미국 광통신 주식의 동반 하락에 대한 우려가 제기되며, 외인 및 기관의 매도세와 프로그램 매매에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['대한광통신', '주가 하락', '미국 광통신']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17050</v>
+        <v>28350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.96%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E18" t="n">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>560</v>
+        <v>199</v>
       </c>
       <c r="H18" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K18" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L18" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M18" t="n">
-        <v>16750</v>
+        <v>28050</v>
       </c>
       <c r="N18" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O18" t="n">
-        <v>96238539370</v>
+        <v>64775735025</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-426000</v>
+        <v>-612000</v>
       </c>
       <c r="S18" t="n">
-        <v>-60000</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대한광통신의 주가 하락 및 미국 광통신 주식의 동반 하락에 대한 우려가 제기되며, 외인 및 기관의 매도세와 프로그램 매매에 대한 불만이 나타남.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대한광통신', '주가 하락', '미국 광통신']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="F19" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="G19" t="n">
-        <v>1328</v>
+        <v>1351</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2174,7 +2174,7 @@
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>210605558150</v>
+        <v>216059947500</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2183,23 +2183,23 @@
         <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-579000</v>
+        <v>-650000</v>
       </c>
       <c r="S19" t="n">
-        <v>-91000</v>
+        <v>-117000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>국내 가스 발전 수주 및 원전 건설 기대 언급, 그러나 주가 하락 및 부정적 전망 제기.</t>
+          <t>해외 발전소 수주 기대감 있으나, 원전 관련 부정적 전망 및 공매도 관련 불만 제기. 주가 하락에 대한 불안감.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '수주']</t>
+          <t>['발전소 수주', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4865</v>
+        <v>4885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.62%</t>
+          <t>'-6.24%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="H20" t="n">
         <v>4.65</v>
@@ -2266,7 +2266,7 @@
         <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>69555206144</v>
+        <v>70270154337</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2275,7 +2275,7 @@
         <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>-237000</v>
+        <v>-106000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15290</v>
+        <v>15340</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.50%</t>
+          <t>'-8.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H21" t="n">
         <v>0.93</v>
@@ -2358,7 +2358,7 @@
         <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>35645875105</v>
+        <v>36057963995</v>
       </c>
       <c r="P21" t="n">
         <v>17590</v>
@@ -2367,7 +2367,7 @@
         <v>6320</v>
       </c>
       <c r="R21" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52700</v>
+        <v>52800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.29%</t>
+          <t>'-9.12%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F22" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G22" t="n">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2450,7 +2450,7 @@
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>56906800150</v>
+        <v>57237746600</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2459,23 +2459,23 @@
         <v>25600</v>
       </c>
       <c r="R22" t="n">
-        <v>-173000</v>
+        <v>-167000</v>
       </c>
       <c r="S22" t="n">
-        <v>-30000</v>
+        <v>-48000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>비만약 승인 및 기술 수출에도 불구하고 급락, 주가 조작 및 개미 털기 의혹 제기.</t>
+          <t>비만약 관련 기술 수출 및 식약처 승인에도 불구하고 주가 급락에 대한 불만. 주가 조작 및 세력 개입 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만약', '기술수출', '주가조작']</t>
+          <t>['기술 수출', '비만약']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7080</v>
+        <v>7060</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.46%</t>
+          <t>'-9.72%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.03</v>
       </c>
       <c r="E23" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F23" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G23" t="n">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="H23" t="n">
         <v>3.09</v>
@@ -2536,13 +2536,13 @@
         <v>8510</v>
       </c>
       <c r="M23" t="n">
-        <v>7050</v>
+        <v>7010</v>
       </c>
       <c r="N23" t="n">
         <v>5.12</v>
       </c>
       <c r="O23" t="n">
-        <v>86423645160</v>
+        <v>87221362690</v>
       </c>
       <c r="P23" t="n">
         <v>23500</v>
@@ -2551,14 +2551,14 @@
         <v>2890</v>
       </c>
       <c r="R23" t="n">
-        <v>-518000</v>
+        <v>-516000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>삼표시멘트의 본PF 대주단 구성 중 소식 및 성수동 땅값 언급. 주가 급등 가능성에 대한 기대와 분석.</t>
+          <t>본PF 대주단 구성 및 심의 통과 관련 정보 언급. 부동산 경기와 연관한 주가 상승 기대와 함께, 경영진 및 주가 흐름에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '땅값']</t>
+          <t>['본PF', '부동산']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9830</v>
+        <v>9840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.72%</t>
+          <t>'-10.63%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>7251422775</v>
+        <v>7280640735</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_14.xlsx
+++ b/data/trending_integrated_20261008_14.xlsx
@@ -578,10 +578,10 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
         <v>210</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31075005960</v>
+        <v>31112234960</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11550</v>
+        <v>14180</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.90%</t>
+          <t>'+18.27%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04</v>
+        <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>273</v>
+        <v>179</v>
       </c>
       <c r="H3" t="n">
-        <v>37.45</v>
+        <v>4.43</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9880</v>
+        <v>11990</v>
       </c>
       <c r="K3" t="n">
-        <v>10030</v>
+        <v>14330</v>
       </c>
       <c r="L3" t="n">
-        <v>11600</v>
+        <v>14980</v>
       </c>
       <c r="M3" t="n">
-        <v>9850</v>
+        <v>13070</v>
       </c>
       <c r="N3" t="n">
-        <v>37.41</v>
+        <v>4.66</v>
       </c>
       <c r="O3" t="n">
-        <v>66258062655</v>
+        <v>52818466795</v>
       </c>
       <c r="P3" t="n">
-        <v>19150</v>
+        <v>14980</v>
       </c>
       <c r="Q3" t="n">
-        <v>3445</v>
+        <v>6500</v>
       </c>
       <c r="R3" t="n">
-        <v>133000</v>
+        <v>-23000</v>
       </c>
       <c r="S3" t="n">
-        <v>508000</v>
+        <v>-39000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전구체', '양극재', '매출']</t>
+          <t>['글라스본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13780</v>
+        <v>11550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.93%</t>
+          <t>'+16.90%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>172</v>
+        <v>284</v>
       </c>
       <c r="H4" t="n">
-        <v>4.43</v>
+        <v>37.45</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11990</v>
+        <v>9880</v>
       </c>
       <c r="K4" t="n">
-        <v>14330</v>
+        <v>10030</v>
       </c>
       <c r="L4" t="n">
-        <v>14980</v>
+        <v>11600</v>
       </c>
       <c r="M4" t="n">
-        <v>13070</v>
+        <v>9850</v>
       </c>
       <c r="N4" t="n">
-        <v>4.66</v>
+        <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>48733675685</v>
+        <v>67360194050</v>
       </c>
       <c r="P4" t="n">
-        <v>14980</v>
+        <v>19150</v>
       </c>
       <c r="Q4" t="n">
-        <v>6500</v>
+        <v>3445</v>
       </c>
       <c r="R4" t="n">
-        <v>-23000</v>
+        <v>133000</v>
       </c>
       <c r="S4" t="n">
-        <v>-39000</v>
+        <v>508000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['글라스본더', '유리기판', '삼성전기']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15280</v>
+        <v>15260</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.80%</t>
+          <t>'+10.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="F5" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G5" t="n">
-        <v>1564</v>
+        <v>1587</v>
       </c>
       <c r="H5" t="n">
         <v>0.09</v>
@@ -886,7 +886,7 @@
         <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>191871310320</v>
+        <v>196352409870</v>
       </c>
       <c r="P5" t="n">
         <v>28700</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13250</v>
+        <v>13200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.41%</t>
+          <t>'+5.01%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="H6" t="n">
         <v>1.07</v>
@@ -978,7 +978,7 @@
         <v>1.88</v>
       </c>
       <c r="O6" t="n">
-        <v>85199505075</v>
+        <v>85579983175</v>
       </c>
       <c r="P6" t="n">
         <v>22250</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유증 물량 정리 및 매물대 언급. 주가 상승에 대한 기대감과 함께, 변동성에 대한 우려와 기대감 혼재.</t>
+          <t>HLB에서 HLB제약으로의 이동 후 상승 기대감. 유증 물량 정리 후 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유증', '매물대']</t>
+          <t>['유증 물량', '상승 기대감', '목표 주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38150</v>
+        <v>38000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+4.97%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H7" t="n">
         <v>31.86</v>
@@ -1070,7 +1070,7 @@
         <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>125372595000</v>
+        <v>126474061600</v>
       </c>
       <c r="P7" t="n">
         <v>45000</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6610</v>
+        <v>6670</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+3.25%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>8390</v>
       </c>
       <c r="M8" t="n">
-        <v>6540</v>
+        <v>6520</v>
       </c>
       <c r="N8" t="n">
         <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>21345967830</v>
+        <v>21500255830</v>
       </c>
       <c r="P8" t="n">
         <v>9680</v>
@@ -1207,184 +1207,184 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46100</v>
+        <v>8270</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.24%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="F9" t="n">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>1228</v>
+        <v>273</v>
       </c>
       <c r="H9" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K9" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L9" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M9" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N9" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O9" t="n">
-        <v>34388506375</v>
+        <v>17704807500</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R9" t="n">
-        <v>-53000</v>
+        <v>-17000</v>
       </c>
       <c r="S9" t="n">
-        <v>-3000</v>
+        <v>149000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 기대감과 2026년 연말 30만 목표 주가가 언급되며, 공매도 세력에 대한 경고와 함께 무상증자 및 신한증권 관련 논의가 있음.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['HLB', '리보세라닙', '공매도']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8280</v>
+        <v>45975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'+0.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>338</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>180</v>
       </c>
       <c r="G10" t="n">
-        <v>268</v>
+        <v>1265</v>
       </c>
       <c r="H10" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8250</v>
+        <v>45900</v>
       </c>
       <c r="K10" t="n">
-        <v>8190</v>
+        <v>45950</v>
       </c>
       <c r="L10" t="n">
-        <v>8320</v>
+        <v>46500</v>
       </c>
       <c r="M10" t="n">
-        <v>8090</v>
+        <v>45100</v>
       </c>
       <c r="N10" t="n">
-        <v>26.55</v>
+        <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>17302844765</v>
+        <v>34955580700</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>8090</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-17000</v>
+        <v>-53000</v>
       </c>
       <c r="S10" t="n">
-        <v>149000</v>
+        <v>-3000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 기대감과 2026년 연말 30만 목표 주가가 언급되며, 공매도 세력에 대한 경고와 함께 무상증자 및 신한증권 관련 논의가 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['HLB', '리보세라닙', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1726000</v>
+        <v>1721000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.17%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G11" t="n">
-        <v>1600</v>
+        <v>1627</v>
       </c>
       <c r="H11" t="n">
         <v>49.59</v>
@@ -1438,7 +1438,7 @@
         <v>49.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3445369388500</v>
+        <v>3507755960500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>267000</v>
+        <v>266250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'-0.84%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G12" t="n">
-        <v>2166</v>
+        <v>2237</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>3597981017250</v>
+        <v>3662669190250</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 증시 상황에 대한 불만 표출. 실적 대비 주가 부양 부재에 대한 비판.</t>
+          <t>낮은 주가와 높은 영업이익 간의 괴리감에 대한 불만 제기. 정부 정책 및 외인 거래에 대한 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주가 부양', '국내 증시']</t>
+          <t>['영업이익', '주가', '정부 정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4365</v>
+        <v>19010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.47%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.19</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="n">
-        <v>193</v>
+        <v>382</v>
       </c>
       <c r="H13" t="n">
-        <v>4.46</v>
+        <v>27.68</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4430</v>
+        <v>19540</v>
       </c>
       <c r="K13" t="n">
-        <v>4650</v>
+        <v>19490</v>
       </c>
       <c r="L13" t="n">
-        <v>4855</v>
+        <v>19500</v>
       </c>
       <c r="M13" t="n">
-        <v>4185</v>
+        <v>18850</v>
       </c>
       <c r="N13" t="n">
-        <v>3.27</v>
+        <v>27.67</v>
       </c>
       <c r="O13" t="n">
-        <v>90441090340</v>
+        <v>45931869650</v>
       </c>
       <c r="P13" t="n">
-        <v>5470</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>2810</v>
+        <v>18440</v>
       </c>
       <c r="R13" t="n">
-        <v>-471000</v>
+        <v>-449000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
+          <t>조선주 주가 하락에 대한 불만 및 실적 발표, 애널리스트 의견에 대한 불신. 주주환원 정책 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', '페스트']</t>
+          <t>['조선주', '실적', '주주환원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18990</v>
+        <v>4310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>1.19</v>
       </c>
       <c r="E14" t="n">
         <v>137</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G14" t="n">
-        <v>376</v>
+        <v>193</v>
       </c>
       <c r="H14" t="n">
-        <v>27.68</v>
+        <v>4.46</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19540</v>
+        <v>4430</v>
       </c>
       <c r="K14" t="n">
-        <v>19490</v>
+        <v>4650</v>
       </c>
       <c r="L14" t="n">
-        <v>19500</v>
+        <v>4855</v>
       </c>
       <c r="M14" t="n">
-        <v>18850</v>
+        <v>4185</v>
       </c>
       <c r="N14" t="n">
-        <v>27.67</v>
+        <v>3.27</v>
       </c>
       <c r="O14" t="n">
-        <v>45275379110</v>
+        <v>90734085855</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>5470</v>
       </c>
       <c r="Q14" t="n">
-        <v>18440</v>
+        <v>2810</v>
       </c>
       <c r="R14" t="n">
-        <v>-449000</v>
+        <v>-471000</v>
       </c>
       <c r="S14" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 폭락 및 실적 기대와 달리 손실 발생, 금리 인상 및 수주 취소 우려 제기.</t>
+          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '수주']</t>
+          <t>['항생제', '폐렴', '페스트']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
         <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>43414994645</v>
+        <v>44116315895</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI가 지목한 JP, 한국, 신한, 삼성증권 등 특정 기관 및 증권사에 대한 의혹 제기. 연기금 및 삼성자산운용의 움직임과 공매도에 대한 불만 표출, 주가 조작 및 개인 투자자 손실에 대한 우려.</t>
+          <t>주가 조작 의혹 제기 및 공매도 과열 종목 지정 촉구. 연기금, 자산운용사의 역할에 대한 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '주가 조작', '연기금']</t>
+          <t>['주가 조작', '공매도', '연기금']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>231500</v>
+        <v>232000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-3.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F16" t="n">
         <v>73</v>
       </c>
       <c r="G16" t="n">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="H16" t="n">
         <v>3.47</v>
@@ -1898,7 +1898,7 @@
         <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>45432856750</v>
+        <v>46008476750</v>
       </c>
       <c r="P16" t="n">
         <v>1233000</v>
@@ -1943,184 +1943,184 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17070</v>
+        <v>28400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.85%</t>
+          <t>'-4.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>570</v>
+        <v>201</v>
       </c>
       <c r="H17" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L17" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M17" t="n">
-        <v>16750</v>
+        <v>28050</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>97116231310</v>
+        <v>65376830925</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>-412000</v>
+        <v>-612000</v>
       </c>
       <c r="S17" t="n">
-        <v>-70000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대한광통신의 주가 하락 및 미국 광통신 주식의 동반 하락에 대한 우려가 제기되며, 외인 및 기관의 매도세와 프로그램 매매에 대한 불만이 나타남.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대한광통신', '주가 하락', '미국 광통신']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28350</v>
+        <v>17080</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.76</v>
+        <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>199</v>
+        <v>574</v>
       </c>
       <c r="H18" t="n">
-        <v>10.02</v>
+        <v>3.97</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29800</v>
+        <v>17940</v>
       </c>
       <c r="K18" t="n">
-        <v>29900</v>
+        <v>17770</v>
       </c>
       <c r="L18" t="n">
-        <v>30000</v>
+        <v>17940</v>
       </c>
       <c r="M18" t="n">
-        <v>28050</v>
+        <v>16750</v>
       </c>
       <c r="N18" t="n">
-        <v>10.78</v>
+        <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>64775735025</v>
+        <v>97894759295</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>15960</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-612000</v>
+        <v>-412000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>-70000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>대한광통신의 주가 하락 및 미국 광통신 주식의 동반 하락에 대한 우려가 제기되며, 외인 및 기관의 매도세와 프로그램 매매에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['대한광통신', '주가 하락', '미국 광통신']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F19" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G19" t="n">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2174,7 +2174,7 @@
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>216059947500</v>
+        <v>224669291050</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>해외 발전소 수주 기대감 있으나, 원전 관련 부정적 전망 및 공매도 관련 불만 제기. 주가 하락에 대한 불안감.</t>
+          <t>미국 텍사스 가스발전 수주 기대감 및 원전 사업 연계 가능성 언급. 공매도에 대한 불만.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['발전소 수주', '공매도']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4885</v>
+        <v>4855</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H20" t="n">
         <v>4.65</v>
@@ -2266,7 +2266,7 @@
         <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>70270154337</v>
+        <v>70714311887</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15340</v>
+        <v>15270</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.20%</t>
+          <t>'-8.62%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2358,7 +2358,7 @@
         <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>36057963995</v>
+        <v>36203670900</v>
       </c>
       <c r="P21" t="n">
         <v>17590</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52800</v>
+        <v>53000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.12%</t>
+          <t>'-8.78%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F22" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G22" t="n">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2450,7 +2450,7 @@
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>57237746600</v>
+        <v>57597861600</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>비만약 관련 기술 수출 및 식약처 승인에도 불구하고 주가 급락에 대한 불만. 주가 조작 및 세력 개입 의혹 제기.</t>
+          <t>비만약 기술 수출 성공에도 불구하고 급락하는 주가에 대한 불만. 주가 조작 및 악질적 흐름 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['기술 수출', '비만약']</t>
+          <t>['기술 수출', '급락', '주가 조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,79 +2495,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7060</v>
+        <v>9830</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.72%</t>
+          <t>'-10.72%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-2.03</v>
+        <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="G23" t="n">
-        <v>602</v>
+        <v>374</v>
       </c>
       <c r="H23" t="n">
-        <v>3.09</v>
+        <v>5.04</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7820</v>
+        <v>11010</v>
       </c>
       <c r="K23" t="n">
-        <v>8080</v>
+        <v>10110</v>
       </c>
       <c r="L23" t="n">
-        <v>8510</v>
+        <v>10130</v>
       </c>
       <c r="M23" t="n">
-        <v>7010</v>
+        <v>9750</v>
       </c>
       <c r="N23" t="n">
-        <v>5.12</v>
+        <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>87221362690</v>
+        <v>7295706275</v>
       </c>
       <c r="P23" t="n">
-        <v>23500</v>
+        <v>15900</v>
       </c>
       <c r="Q23" t="n">
-        <v>2890</v>
+        <v>6310</v>
       </c>
       <c r="R23" t="n">
-        <v>-516000</v>
+        <v>-325000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>본PF 대주단 구성 및 심의 통과 관련 정보 언급. 부동산 경기와 연관한 주가 상승 기대와 함께, 경영진 및 주가 흐름에 대한 불만 표출.</t>
+          <t>미국 항생제 관련주 상승에 대한 언급과 신풍제약의 주가 흐름에 대한 불만. 바이러스 관련주로서의 기대감.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['본PF', '부동산']</t>
+          <t>['항생제', '바이러스', '주가 흐름']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2580,86 +2580,86 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9840</v>
+        <v>6980</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.63%</t>
+          <t>'-10.74%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.03</v>
+        <v>-2.03</v>
       </c>
       <c r="E24" t="n">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="F24" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="G24" t="n">
-        <v>371</v>
+        <v>606</v>
       </c>
       <c r="H24" t="n">
-        <v>5.04</v>
+        <v>3.09</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>11010</v>
+        <v>7820</v>
       </c>
       <c r="K24" t="n">
-        <v>10110</v>
+        <v>8080</v>
       </c>
       <c r="L24" t="n">
-        <v>10130</v>
+        <v>8510</v>
       </c>
       <c r="M24" t="n">
-        <v>9750</v>
+        <v>6910</v>
       </c>
       <c r="N24" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="O24" t="n">
-        <v>7280640735</v>
+        <v>87965227125</v>
       </c>
       <c r="P24" t="n">
-        <v>15900</v>
+        <v>23500</v>
       </c>
       <c r="Q24" t="n">
-        <v>6310</v>
+        <v>2890</v>
       </c>
       <c r="R24" t="n">
-        <v>-325000</v>
+        <v>-516000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>신풍제약 주가 급등 해외 사례 언급, 에볼라 관련 기대감 있으나 매도 의견 및 개인 투자자들의 혼조세 관찰됨.</t>
+          <t>본PF 대주단 구성 및 심의 통과 관련 정보 언급. 부동산 경기와 연관한 주가 상승 기대와 함께, 경영진 및 주가 흐름에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['신풍제약', '항생제', '에볼라']</t>
+          <t>['본PF', '부동산']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>038500</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261008_14.xlsx
+++ b/data/trending_integrated_20261008_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" t="n">
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31112234960</v>
+        <v>31123510930</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14180</v>
+        <v>11470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.27%</t>
+          <t>'+16.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="H3" t="n">
-        <v>4.43</v>
+        <v>37.45</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11990</v>
+        <v>9880</v>
       </c>
       <c r="K3" t="n">
-        <v>14330</v>
+        <v>10030</v>
       </c>
       <c r="L3" t="n">
-        <v>14980</v>
+        <v>11600</v>
       </c>
       <c r="M3" t="n">
-        <v>13070</v>
+        <v>9850</v>
       </c>
       <c r="N3" t="n">
-        <v>4.66</v>
+        <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>52818466795</v>
+        <v>67703134630</v>
       </c>
       <c r="P3" t="n">
-        <v>14980</v>
+        <v>19150</v>
       </c>
       <c r="Q3" t="n">
-        <v>6500</v>
+        <v>3445</v>
       </c>
       <c r="R3" t="n">
-        <v>-23000</v>
+        <v>133000</v>
       </c>
       <c r="S3" t="n">
-        <v>-39000</v>
+        <v>508000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['글라스본더', '유리기판', '삼성전기']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11550</v>
+        <v>66200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.90%</t>
+          <t>'+14.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>349</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="G4" t="n">
-        <v>284</v>
+        <v>717</v>
       </c>
       <c r="H4" t="n">
-        <v>37.45</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9880</v>
+        <v>57700</v>
       </c>
       <c r="K4" t="n">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9850</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>37.41</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>67360194050</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>19150</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>133000</v>
+        <v>-167000</v>
       </c>
       <c r="S4" t="n">
-        <v>508000</v>
+        <v>-48000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
+          <t>비만약 승인 및 기술 수출 관련 내용과 주가 급락에 대한 의문 제기. 주가 조작 및 악질 주식으로 규정.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['전구체', '양극재', '매출']</t>
+          <t>['비만약', '기술수출', '주가조작']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15260</v>
+        <v>13610</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.66%</t>
+          <t>'+13.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.15</v>
+        <v>-0.23</v>
       </c>
       <c r="E5" t="n">
-        <v>594</v>
+        <v>97</v>
       </c>
       <c r="F5" t="n">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>1587</v>
+        <v>183</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>4.43</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13790</v>
+        <v>11990</v>
       </c>
       <c r="K5" t="n">
-        <v>13410</v>
+        <v>14330</v>
       </c>
       <c r="L5" t="n">
-        <v>15960</v>
+        <v>14980</v>
       </c>
       <c r="M5" t="n">
-        <v>11600</v>
+        <v>13070</v>
       </c>
       <c r="N5" t="n">
-        <v>0.24</v>
+        <v>4.66</v>
       </c>
       <c r="O5" t="n">
-        <v>196352409870</v>
+        <v>55994484925</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>14980</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>6500</v>
       </c>
       <c r="R5" t="n">
-        <v>-22000</v>
+        <v>-23000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-39000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>덕산넵코어스의 중복 상장 금지 예외 허용 및 무차별 공매도에 대한 강력한 비판. 국민권익위원회 조사 요청 언급.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['중복상장', '공매도', '권익위']</t>
+          <t>['글라스본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13200</v>
+        <v>14640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.01%</t>
+          <t>'+6.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>125</v>
+        <v>620</v>
       </c>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="G6" t="n">
-        <v>244</v>
+        <v>1613</v>
       </c>
       <c r="H6" t="n">
-        <v>1.07</v>
+        <v>0.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12570</v>
+        <v>13790</v>
       </c>
       <c r="K6" t="n">
-        <v>12970</v>
+        <v>13410</v>
       </c>
       <c r="L6" t="n">
-        <v>14200</v>
+        <v>15960</v>
       </c>
       <c r="M6" t="n">
-        <v>12500</v>
+        <v>11600</v>
       </c>
       <c r="N6" t="n">
-        <v>1.88</v>
+        <v>0.24</v>
       </c>
       <c r="O6" t="n">
-        <v>85579983175</v>
+        <v>205347702380</v>
       </c>
       <c r="P6" t="n">
-        <v>22250</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>6000</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>-550000</v>
+        <v>-22000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HLB에서 HLB제약으로의 이동 후 상승 기대감. 유증 물량 정리 후 추가 상승 가능성 언급.</t>
+          <t>국민권익위 접수 사실 언급. 사기 상장 및 무차별 공매도에 대한 불만 제기. 인공위성 교신 성공 관련 내용.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유증 물량', '상승 기대감', '목표 주가']</t>
+          <t>['사기상장', '공매도', '인공위성']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38000</v>
+        <v>13180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.97%</t>
+          <t>'+4.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="F7" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="H7" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K7" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L7" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N7" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>126474061600</v>
+        <v>86002558115</v>
       </c>
       <c r="P7" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q7" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R7" t="n">
-        <v>247000</v>
+        <v>-550000</v>
       </c>
       <c r="S7" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
+          <t>HLB에서 HLB제약으로의 이동 후 상승 기대감. 유증 물량 정리 후 추가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관 매수', '외국인 매수', '추세']</t>
+          <t>['유증 물량', '상승 기대감', '목표 주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6670</v>
+        <v>37800</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.25%</t>
+          <t>'+4.42%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K8" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L8" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M8" t="n">
-        <v>6520</v>
+        <v>36000</v>
       </c>
       <c r="N8" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O8" t="n">
-        <v>21500255830</v>
+        <v>127428120450</v>
       </c>
       <c r="P8" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q8" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R8" t="n">
-        <v>-28000</v>
+        <v>247000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
+          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
+          <t>['기관 매수', '외국인 매수', '추세']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8270</v>
+        <v>6660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.24%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="H9" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8250</v>
+        <v>6460</v>
       </c>
       <c r="K9" t="n">
-        <v>8190</v>
+        <v>6930</v>
       </c>
       <c r="L9" t="n">
-        <v>8320</v>
+        <v>8390</v>
       </c>
       <c r="M9" t="n">
-        <v>8090</v>
+        <v>6520</v>
       </c>
       <c r="N9" t="n">
-        <v>26.55</v>
+        <v>0.31</v>
       </c>
       <c r="O9" t="n">
-        <v>17704807500</v>
+        <v>21623720940</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>9680</v>
       </c>
       <c r="Q9" t="n">
-        <v>8090</v>
+        <v>371</v>
       </c>
       <c r="R9" t="n">
-        <v>-17000</v>
+        <v>-28000</v>
       </c>
       <c r="S9" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45975</v>
+        <v>46100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="F10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G10" t="n">
-        <v>1265</v>
+        <v>1285</v>
       </c>
       <c r="H10" t="n">
         <v>13.39</v>
@@ -1346,7 +1346,7 @@
         <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>34955580700</v>
+        <v>36114683675</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1721000</v>
+        <v>8280</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'+0.36%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.12</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>450</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
-        <v>1627</v>
+        <v>282</v>
       </c>
       <c r="H11" t="n">
-        <v>49.59</v>
+        <v>26.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1723000</v>
+        <v>8250</v>
       </c>
       <c r="K11" t="n">
-        <v>1722000</v>
+        <v>8190</v>
       </c>
       <c r="L11" t="n">
-        <v>1759000</v>
+        <v>8320</v>
       </c>
       <c r="M11" t="n">
-        <v>1692000</v>
+        <v>8090</v>
       </c>
       <c r="N11" t="n">
-        <v>49.71</v>
+        <v>26.55</v>
       </c>
       <c r="O11" t="n">
-        <v>3507755960500</v>
+        <v>18155890430</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>8090</v>
       </c>
       <c r="R11" t="n">
-        <v>17000</v>
+        <v>-17000</v>
       </c>
       <c r="S11" t="n">
-        <v>-84000</v>
+        <v>149000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란 및 주가 조작 의혹 제기, 외국인 매도세 확인.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '외국인']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>266250</v>
+        <v>1712000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-0.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>537</v>
+        <v>449</v>
       </c>
       <c r="G12" t="n">
-        <v>2237</v>
+        <v>1625</v>
       </c>
       <c r="H12" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>268500</v>
+        <v>1723000</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>1722000</v>
       </c>
       <c r="L12" t="n">
-        <v>270000</v>
+        <v>1759000</v>
       </c>
       <c r="M12" t="n">
-        <v>263000</v>
+        <v>1692000</v>
       </c>
       <c r="N12" t="n">
-        <v>46.37</v>
+        <v>49.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3662669190250</v>
+        <v>3604601216000</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>56000</v>
+        <v>17000</v>
       </c>
       <c r="S12" t="n">
-        <v>-965000</v>
+        <v>-84000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>낮은 주가와 높은 영업이익 간의 괴리감에 대한 불만 제기. 정부 정책 및 외인 거래에 대한 비판.</t>
+          <t>솔리다임 상장 관련 최태원 회장에 대한 해명 요구. 이재명 정부와 코스피 시장에 대한 부정적 평가.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주가', '정부 정책']</t>
+          <t>['솔리다임', '상장', '코스피']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19010</v>
+        <v>265500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="G13" t="n">
-        <v>382</v>
+        <v>2233</v>
       </c>
       <c r="H13" t="n">
-        <v>27.68</v>
+        <v>46.38</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19540</v>
+        <v>268500</v>
       </c>
       <c r="K13" t="n">
-        <v>19490</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>19500</v>
+        <v>270000</v>
       </c>
       <c r="M13" t="n">
-        <v>18850</v>
+        <v>263000</v>
       </c>
       <c r="N13" t="n">
-        <v>27.67</v>
+        <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>45931869650</v>
+        <v>3729818461750</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>18440</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-449000</v>
+        <v>56000</v>
       </c>
       <c r="S13" t="n">
-        <v>-78000</v>
+        <v>-965000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조선주 주가 하락에 대한 불만 및 실적 발표, 애널리스트 의견에 대한 불신. 주주환원 정책 요구.</t>
+          <t>영업이익이 높음에도 불구하고 주가 부양이 없다는 불만 제기. 이재명 정부와 국장에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '주주환원']</t>
+          <t>['영업이익', '주가부양', '국장']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4310</v>
+        <v>19030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.19</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F14" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>193</v>
+        <v>382</v>
       </c>
       <c r="H14" t="n">
-        <v>4.46</v>
+        <v>27.68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4430</v>
+        <v>19540</v>
       </c>
       <c r="K14" t="n">
-        <v>4650</v>
+        <v>19490</v>
       </c>
       <c r="L14" t="n">
-        <v>4855</v>
+        <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>4185</v>
+        <v>18850</v>
       </c>
       <c r="N14" t="n">
-        <v>3.27</v>
+        <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>90734085855</v>
+        <v>46755622055</v>
       </c>
       <c r="P14" t="n">
-        <v>5470</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>2810</v>
+        <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>-471000</v>
+        <v>-449000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
+          <t>조선주 주가 하락에 대한 불만 및 실적 발표, 애널리스트 의견에 대한 불신. 주주환원 정책 요구.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', '페스트']</t>
+          <t>['조선주', '실적', '주주환원']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16780</v>
+        <v>234500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.23%</t>
+          <t>'-2.70%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>-0.65</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>637</v>
+        <v>863</v>
       </c>
       <c r="H15" t="n">
-        <v>9.460000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17340</v>
+        <v>241000</v>
       </c>
       <c r="K15" t="n">
-        <v>17190</v>
+        <v>227000</v>
       </c>
       <c r="L15" t="n">
-        <v>17220</v>
+        <v>239500</v>
       </c>
       <c r="M15" t="n">
-        <v>16660</v>
+        <v>210500</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="O15" t="n">
-        <v>44116315895</v>
+        <v>47715410250</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>1233000</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>120000</v>
       </c>
       <c r="R15" t="n">
-        <v>-58000</v>
+        <v>6000</v>
       </c>
       <c r="S15" t="n">
-        <v>-36000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 공매도 과열 종목 지정 촉구. 연기금, 자산운용사의 역할에 대한 비판.</t>
+          <t>공매도 과열 종목 지정 및 연기금 매수세 확인. 신규 계약 공시 및 바이오 업황 호조 기대감. 3연상 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '연기금']</t>
+          <t>['공매도 금지', '계약 공시', '바이오']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,86 +1844,86 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>232000</v>
+        <v>4295</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.73%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.65</v>
+        <v>1.19</v>
       </c>
       <c r="E16" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G16" t="n">
-        <v>832</v>
+        <v>196</v>
       </c>
       <c r="H16" t="n">
-        <v>3.47</v>
+        <v>4.46</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>241000</v>
+        <v>4430</v>
       </c>
       <c r="K16" t="n">
-        <v>227000</v>
+        <v>4650</v>
       </c>
       <c r="L16" t="n">
-        <v>239500</v>
+        <v>4855</v>
       </c>
       <c r="M16" t="n">
-        <v>210500</v>
+        <v>4185</v>
       </c>
       <c r="N16" t="n">
-        <v>4.12</v>
+        <v>3.27</v>
       </c>
       <c r="O16" t="n">
-        <v>46008476750</v>
+        <v>91009861570</v>
       </c>
       <c r="P16" t="n">
-        <v>1233000</v>
+        <v>5470</v>
       </c>
       <c r="Q16" t="n">
-        <v>120000</v>
+        <v>2810</v>
       </c>
       <c r="R16" t="n">
-        <v>6000</v>
+        <v>-471000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 연기금 매수세 확인. 신규 계약 공시 및 바이오 업황 호조 기대감. 3연상 기대감.</t>
+          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도 금지', '계약 공시', '바이오']</t>
+          <t>['항생제', '폐렴', '페스트']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28400</v>
+        <v>16800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.70%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>-0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G17" t="n">
-        <v>201</v>
+        <v>641</v>
       </c>
       <c r="H17" t="n">
-        <v>10.02</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>17340</v>
       </c>
       <c r="K17" t="n">
-        <v>29900</v>
+        <v>17190</v>
       </c>
       <c r="L17" t="n">
-        <v>30000</v>
+        <v>17220</v>
       </c>
       <c r="M17" t="n">
-        <v>28050</v>
+        <v>16660</v>
       </c>
       <c r="N17" t="n">
-        <v>10.78</v>
+        <v>9.5</v>
       </c>
       <c r="O17" t="n">
-        <v>65376830925</v>
+        <v>44901259755</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-612000</v>
+        <v>-58000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>-36000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>주가 조작 의혹 제기 및 공매도 과열 종목 지정 촉구. 연기금, 자산운용사의 역할에 대한 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['주가 조작', '공매도', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17080</v>
+        <v>17060</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.91%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="n">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>97894759295</v>
+        <v>98944799930</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대한광통신의 주가 하락 및 미국 광통신 주식의 동반 하락에 대한 우려가 제기되며, 외인 및 기관의 매도세와 프로그램 매매에 대한 불만이 나타남.</t>
+          <t>미국 광통신 주가 하락에 따른 우려 제기. 외인 및 기관의 쌍매도 상황 언급. 주가에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대한광통신', '주가 하락', '미국 광통신']</t>
+          <t>['광통신', '쌍매도', '주가하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75500</v>
+        <v>28200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.21%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.76</v>
       </c>
       <c r="E19" t="n">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>271</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>1364</v>
+        <v>203</v>
       </c>
       <c r="H19" t="n">
-        <v>22.49</v>
+        <v>10.02</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>80500</v>
+        <v>29800</v>
       </c>
       <c r="K19" t="n">
-        <v>79600</v>
+        <v>29900</v>
       </c>
       <c r="L19" t="n">
-        <v>79600</v>
+        <v>30000</v>
       </c>
       <c r="M19" t="n">
-        <v>75200</v>
+        <v>28050</v>
       </c>
       <c r="N19" t="n">
-        <v>22.59</v>
+        <v>10.78</v>
       </c>
       <c r="O19" t="n">
-        <v>224669291050</v>
+        <v>67126984350</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>75900</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>15960</v>
       </c>
       <c r="R19" t="n">
-        <v>-650000</v>
+        <v>-612000</v>
       </c>
       <c r="S19" t="n">
-        <v>-117000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 텍사스 가스발전 수주 기대감 및 원전 사업 연계 가능성 언급. 공매도에 대한 불만.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,135 +2207,135 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4855</v>
+        <v>75400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>458</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>274</v>
       </c>
       <c r="G20" t="n">
-        <v>338</v>
+        <v>1393</v>
       </c>
       <c r="H20" t="n">
-        <v>4.65</v>
+        <v>22.49</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5210</v>
+        <v>80500</v>
       </c>
       <c r="K20" t="n">
-        <v>5220</v>
+        <v>79600</v>
       </c>
       <c r="L20" t="n">
-        <v>5310</v>
+        <v>79600</v>
       </c>
       <c r="M20" t="n">
-        <v>4755</v>
+        <v>75200</v>
       </c>
       <c r="N20" t="n">
-        <v>4.72</v>
+        <v>22.59</v>
       </c>
       <c r="O20" t="n">
-        <v>70714311887</v>
+        <v>228056501550</v>
       </c>
       <c r="P20" t="n">
-        <v>8100</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>592</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-106000</v>
+        <v>-650000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-117000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
+          <t>한미 텍사스 가스발전 관련 소식 언급. 공매도에 대한 불만과 원전에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '광트랜시버', '장내매도']</t>
+          <t>['가스발전', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15270</v>
+        <v>4855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.62%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.44</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="H21" t="n">
-        <v>0.93</v>
+        <v>4.65</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>16710</v>
+        <v>5210</v>
       </c>
       <c r="K21" t="n">
-        <v>16460</v>
+        <v>5220</v>
       </c>
       <c r="L21" t="n">
-        <v>17180</v>
+        <v>5310</v>
       </c>
       <c r="M21" t="n">
-        <v>14820</v>
+        <v>4755</v>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>36203670900</v>
+        <v>71143086744</v>
       </c>
       <c r="P21" t="n">
-        <v>17590</v>
+        <v>8100</v>
       </c>
       <c r="Q21" t="n">
-        <v>6320</v>
+        <v>592</v>
       </c>
       <c r="R21" t="n">
-        <v>10000</v>
+        <v>-106000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['전환사채', '광트랜시버', '장내매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,99 +2396,99 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53000</v>
+        <v>15290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.78%</t>
+          <t>'-8.50%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.02</v>
+        <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>349</v>
+        <v>61</v>
       </c>
       <c r="F22" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>706</v>
+        <v>205</v>
       </c>
       <c r="H22" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>58100</v>
+        <v>16710</v>
       </c>
       <c r="K22" t="n">
-        <v>63200</v>
+        <v>16460</v>
       </c>
       <c r="L22" t="n">
-        <v>63800</v>
+        <v>17180</v>
       </c>
       <c r="M22" t="n">
-        <v>51700</v>
+        <v>14820</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>57597861600</v>
+        <v>36381334265</v>
       </c>
       <c r="P22" t="n">
-        <v>63800</v>
+        <v>17590</v>
       </c>
       <c r="Q22" t="n">
-        <v>25600</v>
+        <v>6320</v>
       </c>
       <c r="R22" t="n">
-        <v>-167000</v>
+        <v>10000</v>
       </c>
       <c r="S22" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>비만약 기술 수출 성공에도 불구하고 급락하는 주가에 대한 불만. 주가 조작 및 악질적 흐름 비판.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['기술 수출', '급락', '주가 조작']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9830</v>
+        <v>9840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.72%</t>
+          <t>'-10.63%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" t="n">
         <v>67</v>
       </c>
       <c r="G23" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H23" t="n">
         <v>5.04</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>7295706275</v>
+        <v>7345025255</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6980</v>
+        <v>6940</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.74%</t>
+          <t>'-11.25%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-2.03</v>
       </c>
       <c r="E24" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F24" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="H24" t="n">
         <v>3.09</v>
@@ -2628,13 +2628,13 @@
         <v>8510</v>
       </c>
       <c r="M24" t="n">
-        <v>6910</v>
+        <v>6870</v>
       </c>
       <c r="N24" t="n">
         <v>5.12</v>
       </c>
       <c r="O24" t="n">
-        <v>87965227125</v>
+        <v>89288941440</v>
       </c>
       <c r="P24" t="n">
         <v>23500</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>본PF 대주단 구성 및 심의 통과 관련 정보 언급. 부동산 경기와 연관한 주가 상승 기대와 함께, 경영진 및 주가 흐름에 대한 불만 표출.</t>
+          <t>본PF 대주단 구성 및 심의 통과 관련 정보 언급. 주가 하락 및 물량 관리, 개미 털기에 대한 비판.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['본PF', '부동산']</t>
+          <t>['본PF', '대주단', '물량관리']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20261008_14.xlsx
+++ b/data/trending_integrated_20261008_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31123510930</v>
+        <v>32683978750</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11470</v>
+        <v>11410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.09%</t>
+          <t>'+15.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>67703134630</v>
+        <v>68434753935</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66200</v>
+        <v>13650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.73%</t>
+          <t>'+13.84%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>349</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>717</v>
+        <v>198</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>4.43</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>57700</v>
+        <v>11990</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>14330</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>13070</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>57839661365</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="R4" t="n">
-        <v>-167000</v>
+        <v>-23000</v>
       </c>
       <c r="S4" t="n">
-        <v>-48000</v>
+        <v>-39000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>비만약 승인 및 기술 수출 관련 내용과 주가 급락에 대한 의문 제기. 주가 조작 및 악질 주식으로 규정.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['비만약', '기술수출', '주가조작']</t>
+          <t>['글라스본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,43 +827,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13610</v>
+        <v>14700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.51%</t>
+          <t>'+6.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>640</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>264</v>
       </c>
       <c r="G5" t="n">
-        <v>183</v>
+        <v>1649</v>
       </c>
       <c r="H5" t="n">
-        <v>4.43</v>
+        <v>0.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11990</v>
+        <v>13790</v>
       </c>
       <c r="K5" t="n">
-        <v>14330</v>
+        <v>13410</v>
       </c>
       <c r="L5" t="n">
-        <v>14980</v>
+        <v>15960</v>
       </c>
       <c r="M5" t="n">
-        <v>13070</v>
+        <v>11600</v>
       </c>
       <c r="N5" t="n">
-        <v>4.66</v>
+        <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>55994484925</v>
+        <v>210505841360</v>
       </c>
       <c r="P5" t="n">
-        <v>14980</v>
+        <v>28700</v>
       </c>
       <c r="Q5" t="n">
-        <v>6500</v>
+        <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>-23000</v>
+        <v>-22000</v>
       </c>
       <c r="S5" t="n">
-        <v>-39000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
+          <t>국민권익위 접수 사실 언급. 사기 상장 및 무차별 공매도에 대한 불만 제기. 인공위성 교신 성공 관련 내용.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['글라스본더', '유리기판', '삼성전기']</t>
+          <t>['사기상장', '공매도', '인공위성']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14640</v>
+        <v>13180</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.16%</t>
+          <t>'+4.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>620</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
-        <v>259</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>1613</v>
+        <v>261</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09</v>
+        <v>1.07</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13790</v>
+        <v>12570</v>
       </c>
       <c r="K6" t="n">
-        <v>13410</v>
+        <v>12970</v>
       </c>
       <c r="L6" t="n">
-        <v>15960</v>
+        <v>14200</v>
       </c>
       <c r="M6" t="n">
-        <v>11600</v>
+        <v>12500</v>
       </c>
       <c r="N6" t="n">
-        <v>0.24</v>
+        <v>1.88</v>
       </c>
       <c r="O6" t="n">
-        <v>205347702380</v>
+        <v>86264392535</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>22250</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>6000</v>
       </c>
       <c r="R6" t="n">
-        <v>-22000</v>
+        <v>-550000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국민권익위 접수 사실 언급. 사기 상장 및 무차별 공매도에 대한 불만 제기. 인공위성 교신 성공 관련 내용.</t>
+          <t>HLB 제약의 목표 주가와 유증 물량 정리 후 주가 상승 기대감. 공매도 세력과의 대결 및 바이오 섹터 내에서의 위치 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['사기상장', '공매도', '인공위성']</t>
+          <t>['유증', '목표 주가', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13180</v>
+        <v>37650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.85%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="F7" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>14200</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>86002558115</v>
+        <v>128799028900</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-550000</v>
+        <v>247000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB에서 HLB제약으로의 이동 후 상승 기대감. 유증 물량 정리 후 추가 상승 가능성 언급.</t>
+          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유증 물량', '상승 기대감', '목표 주가']</t>
+          <t>['기관 매수', '외국인 매수', '추세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37800</v>
+        <v>6680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.42%</t>
+          <t>'+3.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="H8" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K8" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L8" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M8" t="n">
-        <v>36000</v>
+        <v>6520</v>
       </c>
       <c r="N8" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>127428120450</v>
+        <v>21699732280</v>
       </c>
       <c r="P8" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q8" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R8" t="n">
-        <v>247000</v>
+        <v>-28000</v>
       </c>
       <c r="S8" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
+          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관 매수', '외국인 매수', '추세']</t>
+          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6660</v>
+        <v>45925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+0.05%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.31</v>
+        <v>-0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>355</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>184</v>
       </c>
       <c r="G9" t="n">
-        <v>230</v>
+        <v>1323</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,183 +1239,183 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6460</v>
+        <v>45900</v>
       </c>
       <c r="K9" t="n">
-        <v>6930</v>
+        <v>45950</v>
       </c>
       <c r="L9" t="n">
-        <v>8390</v>
+        <v>46500</v>
       </c>
       <c r="M9" t="n">
-        <v>6520</v>
+        <v>45100</v>
       </c>
       <c r="N9" t="n">
-        <v>0.31</v>
+        <v>14.12</v>
       </c>
       <c r="O9" t="n">
-        <v>21623720940</v>
+        <v>36438713475</v>
       </c>
       <c r="P9" t="n">
-        <v>9680</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>371</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-28000</v>
+        <v>-53000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 및 FDA 승인 기대감. 무상증자 가능성 언급과 함께 공매도 세력의 발악을 언급하며 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
+          <t>['리보세라닙', 'FDA 승인', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46100</v>
+        <v>8240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>347</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>1285</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K10" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L10" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M10" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>36114683675</v>
+        <v>18840882910</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R10" t="n">
-        <v>-53000</v>
+        <v>-17000</v>
       </c>
       <c r="S10" t="n">
-        <v>-3000</v>
+        <v>149000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 기대감과 2026년 연말 30만 목표 주가가 언급되며, 공매도 세력에 대한 경고와 함께 무상증자 및 신한증권 관련 논의가 있음.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['HLB', '리보세라닙', '공매도']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8280</v>
+        <v>1706000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.36%</t>
+          <t>'-0.99%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>452</v>
       </c>
       <c r="G11" t="n">
-        <v>282</v>
+        <v>1611</v>
       </c>
       <c r="H11" t="n">
-        <v>26.38</v>
+        <v>49.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8250</v>
+        <v>1723000</v>
       </c>
       <c r="K11" t="n">
-        <v>8190</v>
+        <v>1722000</v>
       </c>
       <c r="L11" t="n">
-        <v>8320</v>
+        <v>1759000</v>
       </c>
       <c r="M11" t="n">
-        <v>8090</v>
+        <v>1692000</v>
       </c>
       <c r="N11" t="n">
-        <v>26.55</v>
+        <v>49.71</v>
       </c>
       <c r="O11" t="n">
-        <v>18155890430</v>
+        <v>3683869788000</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>8090</v>
+        <v>403000</v>
       </c>
       <c r="R11" t="n">
-        <v>-17000</v>
+        <v>17000</v>
       </c>
       <c r="S11" t="n">
-        <v>149000</v>
+        <v>-84000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>솔리다임 상장 관련 최태원 회장에 대한 해명 요구. 이재명 정부와 코스피 시장에 대한 부정적 평가.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['솔리다임', '상장', '코스피']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1712000</v>
+        <v>264750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>449</v>
+        <v>543</v>
       </c>
       <c r="G12" t="n">
-        <v>1625</v>
+        <v>2293</v>
       </c>
       <c r="H12" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1723000</v>
+        <v>268500</v>
       </c>
       <c r="K12" t="n">
-        <v>1722000</v>
+        <v>269500</v>
       </c>
       <c r="L12" t="n">
-        <v>1759000</v>
+        <v>270000</v>
       </c>
       <c r="M12" t="n">
-        <v>1692000</v>
+        <v>263000</v>
       </c>
       <c r="N12" t="n">
-        <v>49.71</v>
+        <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>3604601216000</v>
+        <v>3856889094750</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>17000</v>
+        <v>56000</v>
       </c>
       <c r="S12" t="n">
-        <v>-84000</v>
+        <v>-965000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 최태원 회장에 대한 해명 요구. 이재명 정부와 코스피 시장에 대한 부정적 평가.</t>
+          <t>영업이익 최상위에도 불구하고 주가 부양 없는 증시에 대한 불만 표출. 레버리지 투자와 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장', '코스피']</t>
+          <t>['영업이익', '주가 부양', '레버리지']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>265500</v>
+        <v>4340</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-2.03%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>548</v>
+        <v>89</v>
       </c>
       <c r="G13" t="n">
-        <v>2233</v>
+        <v>199</v>
       </c>
       <c r="H13" t="n">
-        <v>46.38</v>
+        <v>4.46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>268500</v>
+        <v>4430</v>
       </c>
       <c r="K13" t="n">
-        <v>269500</v>
+        <v>4650</v>
       </c>
       <c r="L13" t="n">
-        <v>270000</v>
+        <v>4855</v>
       </c>
       <c r="M13" t="n">
-        <v>263000</v>
+        <v>4185</v>
       </c>
       <c r="N13" t="n">
-        <v>46.37</v>
+        <v>3.27</v>
       </c>
       <c r="O13" t="n">
-        <v>3729818461750</v>
+        <v>91286531008</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>5470</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>2810</v>
       </c>
       <c r="R13" t="n">
-        <v>56000</v>
+        <v>-471000</v>
       </c>
       <c r="S13" t="n">
-        <v>-965000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>영업이익이 높음에도 불구하고 주가 부양이 없다는 불만 제기. 이재명 정부와 국장에 대한 부정적 인식.</t>
+          <t>미국 항생제 회사 주가 폭등 속 전염병 관련 뉴스 언급. 국제약품의 대장주 여부 및 금일 시가 지지 여부에 관심.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주가부양', '국장']</t>
+          <t>['항생제', '전염병', '대장주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19030</v>
+        <v>18975</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-2.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>46755622055</v>
+        <v>47984395090</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 주가 하락에 대한 불만 및 실적 발표, 애널리스트 의견에 대한 불신. 주주환원 정책 요구.</t>
+          <t>증권사 애널리스트들의 추천 및 조선주 폭락 원인에 대한 불신 표출. 5개월간의 주가 하락세와 폐업 가능성 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '주주환원']</t>
+          <t>['조선주', '주가 하락', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>234500</v>
+        <v>232500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.70%</t>
+          <t>'-3.53%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.65</v>
       </c>
       <c r="E15" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>863</v>
+        <v>882</v>
       </c>
       <c r="H15" t="n">
         <v>3.47</v>
@@ -1806,7 +1806,7 @@
         <v>4.12</v>
       </c>
       <c r="O15" t="n">
-        <v>47715410250</v>
+        <v>49276113750</v>
       </c>
       <c r="P15" t="n">
         <v>1233000</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 연기금 매수세 확인. 신규 계약 공시 및 바이오 업황 호조 기대감. 3연상 기대감.</t>
+          <t>연기금의 7일째 매수세와 함께 삼천당제약의 아일리아 영업이익 및 캐나다 세마 출시 기대. 공매도 금지 조치와 릴레이 계약 공시 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도 금지', '계약 공시', '바이오']</t>
+          <t>['아일리아', '영업이익', '공매도 금지']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4295</v>
+        <v>16710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.19</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="G16" t="n">
-        <v>196</v>
+        <v>652</v>
       </c>
       <c r="H16" t="n">
-        <v>4.46</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4430</v>
+        <v>17340</v>
       </c>
       <c r="K16" t="n">
-        <v>4650</v>
+        <v>17190</v>
       </c>
       <c r="L16" t="n">
-        <v>4855</v>
+        <v>17220</v>
       </c>
       <c r="M16" t="n">
-        <v>4185</v>
+        <v>16660</v>
       </c>
       <c r="N16" t="n">
-        <v>3.27</v>
+        <v>9.5</v>
       </c>
       <c r="O16" t="n">
-        <v>91009861570</v>
+        <v>46156380585</v>
       </c>
       <c r="P16" t="n">
-        <v>5470</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-471000</v>
+        <v>-58000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 폭등 및 WHO의 러시아 폐렴 상황 파악 지연 소식에 따른 관심 증가. 페스트 관련 보도도 영향.</t>
+          <t>개인 투자자가 돈을 못 버는 이유 분석 및 주가 조작 의혹 제기. 대우건설 주주들에게 대차 해지의 중요성 강조.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['항생제', '폐렴', '페스트']</t>
+          <t>['주가 조작', '공매도', '대차 해지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16800</v>
+        <v>17020</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.11%</t>
+          <t>'-5.13%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>-0.95</v>
       </c>
       <c r="E17" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="F17" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G17" t="n">
-        <v>641</v>
+        <v>591</v>
       </c>
       <c r="H17" t="n">
-        <v>9.460000000000001</v>
+        <v>3.97</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17340</v>
+        <v>17940</v>
       </c>
       <c r="K17" t="n">
-        <v>17190</v>
+        <v>17770</v>
       </c>
       <c r="L17" t="n">
-        <v>17220</v>
+        <v>17940</v>
       </c>
       <c r="M17" t="n">
-        <v>16660</v>
+        <v>16750</v>
       </c>
       <c r="N17" t="n">
-        <v>9.5</v>
+        <v>4.92</v>
       </c>
       <c r="O17" t="n">
-        <v>44901259755</v>
+        <v>100339643435</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R17" t="n">
-        <v>-58000</v>
+        <v>-412000</v>
       </c>
       <c r="S17" t="n">
-        <v>-36000</v>
+        <v>-70000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 제기 및 공매도 과열 종목 지정 촉구. 연기금, 자산운용사의 역할에 대한 비판.</t>
+          <t>미국 광통신 주가 하락에 따른 우려 제기. 외인 및 기관의 쌍매도 상황 언급. 주가에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '연기금']</t>
+          <t>['광통신', '쌍매도', '주가하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,130 +2028,130 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17060</v>
+        <v>28200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E18" t="n">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>584</v>
+        <v>209</v>
       </c>
       <c r="H18" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K18" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L18" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M18" t="n">
-        <v>16750</v>
+        <v>28050</v>
       </c>
       <c r="N18" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O18" t="n">
-        <v>98944799930</v>
+        <v>68408236400</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-412000</v>
+        <v>-612000</v>
       </c>
       <c r="S18" t="n">
-        <v>-70000</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 하락에 따른 우려 제기. 외인 및 기관의 쌍매도 상황 언급. 주가에 대한 부정적 전망.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '쌍매도', '주가하락']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28200</v>
+        <v>75300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-6.46%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.76</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>465</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>279</v>
       </c>
       <c r="G19" t="n">
-        <v>203</v>
+        <v>1449</v>
       </c>
       <c r="H19" t="n">
-        <v>10.02</v>
+        <v>22.49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29800</v>
+        <v>80500</v>
       </c>
       <c r="K19" t="n">
-        <v>29900</v>
+        <v>79600</v>
       </c>
       <c r="L19" t="n">
-        <v>30000</v>
+        <v>79600</v>
       </c>
       <c r="M19" t="n">
-        <v>28050</v>
+        <v>75200</v>
       </c>
       <c r="N19" t="n">
-        <v>10.78</v>
+        <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>67126984350</v>
+        <v>235140293350</v>
       </c>
       <c r="P19" t="n">
-        <v>75900</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>15960</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-612000</v>
+        <v>-650000</v>
       </c>
       <c r="S19" t="n">
-        <v>1000</v>
+        <v>-117000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>한미 텍사스 가스 발전 확정 소식과 함께 공매도에 대한 불만 제기. 연말 수익률 및 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['가스 발전', '공매도', '수익률']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2207,135 +2207,135 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75400</v>
+        <v>4845</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-7.01%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>458</v>
+        <v>94</v>
       </c>
       <c r="F20" t="n">
-        <v>274</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>1393</v>
+        <v>343</v>
       </c>
       <c r="H20" t="n">
-        <v>22.49</v>
+        <v>4.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>80500</v>
+        <v>5210</v>
       </c>
       <c r="K20" t="n">
-        <v>79600</v>
+        <v>5220</v>
       </c>
       <c r="L20" t="n">
-        <v>79600</v>
+        <v>5310</v>
       </c>
       <c r="M20" t="n">
-        <v>75200</v>
+        <v>4755</v>
       </c>
       <c r="N20" t="n">
-        <v>22.59</v>
+        <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>228056501550</v>
+        <v>71843067955</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>-650000</v>
+        <v>-106000</v>
       </c>
       <c r="S20" t="n">
-        <v>-117000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>한미 텍사스 가스발전 관련 소식 언급. 공매도에 대한 불만과 원전에 대한 부정적 전망.</t>
+          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가스발전', '공매도', '원전']</t>
+          <t>['전환사채', '광트랜시버', '장내매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4855</v>
+        <v>15250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-8.74%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.44</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>340</v>
+        <v>205</v>
       </c>
       <c r="H21" t="n">
-        <v>4.65</v>
+        <v>0.93</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5210</v>
+        <v>16710</v>
       </c>
       <c r="K21" t="n">
-        <v>5220</v>
+        <v>16460</v>
       </c>
       <c r="L21" t="n">
-        <v>5310</v>
+        <v>17180</v>
       </c>
       <c r="M21" t="n">
-        <v>4755</v>
+        <v>14820</v>
       </c>
       <c r="N21" t="n">
-        <v>4.72</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>71143086744</v>
+        <v>36611745100</v>
       </c>
       <c r="P21" t="n">
-        <v>8100</v>
+        <v>17590</v>
       </c>
       <c r="Q21" t="n">
-        <v>592</v>
+        <v>6320</v>
       </c>
       <c r="R21" t="n">
-        <v>-106000</v>
+        <v>10000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '광트랜시버', '장내매도']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,99 +2396,99 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15290</v>
+        <v>52600</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.50%</t>
+          <t>'-9.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.44</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>351</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="G22" t="n">
-        <v>205</v>
+        <v>722</v>
       </c>
       <c r="H22" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>16710</v>
+        <v>58100</v>
       </c>
       <c r="K22" t="n">
-        <v>16460</v>
+        <v>63200</v>
       </c>
       <c r="L22" t="n">
-        <v>17180</v>
+        <v>63800</v>
       </c>
       <c r="M22" t="n">
-        <v>14820</v>
+        <v>51700</v>
       </c>
       <c r="N22" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>36381334265</v>
+        <v>58352686900</v>
       </c>
       <c r="P22" t="n">
-        <v>17590</v>
+        <v>63800</v>
       </c>
       <c r="Q22" t="n">
-        <v>6320</v>
+        <v>25600</v>
       </c>
       <c r="R22" t="n">
-        <v>10000</v>
+        <v>-167000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>비만약 승인 및 기술 수출 관련 내용과 주가 급락에 대한 의문 제기. 주가 조작 및 악질 주식으로 규정.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['비만약', '기술수출', '주가조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2499,18 +2499,18 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9840</v>
+        <v>9810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.63%</t>
+          <t>'-10.90%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
         <v>67</v>
@@ -2542,7 +2542,7 @@
         <v>5.01</v>
       </c>
       <c r="O23" t="n">
-        <v>7345025255</v>
+        <v>7392578745</v>
       </c>
       <c r="P23" t="n">
         <v>15900</v>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6940</v>
+        <v>6930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-11.25%</t>
+          <t>'-11.38%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2605,10 +2605,10 @@
         <v>226</v>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G24" t="n">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="H24" t="n">
         <v>3.09</v>
@@ -2634,7 +2634,7 @@
         <v>5.12</v>
       </c>
       <c r="O24" t="n">
-        <v>89288941440</v>
+        <v>89750066215</v>
       </c>
       <c r="P24" t="n">
         <v>23500</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>본PF 대주단 구성 및 심의 통과 관련 정보 언급. 주가 하락 및 물량 관리, 개미 털기에 대한 비판.</t>
+          <t>프로젝트 파이낸싱(PF) 대주단 구성 중이며, 부동산 시장 상황에 따른 증시 흐름 언급. 개미 투자자의 매수세와 주가 운전 방식에 대한 의구심.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '물량관리']</t>
+          <t>['프로젝트 파이낸싱', '부동산', '주가 운전']</t>
         </is>
       </c>
       <c r="X24" t="n">
